--- a/samples/2026_생태탐험_7점척도_NPS.xlsx
+++ b/samples/2026_생태탐험_7점척도_NPS.xlsx
@@ -4,6 +4,8 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="응답" sheetId="1" r:id="rId1"/>
+    <sheet name="사업정보" sheetId="2" r:id="rId2"/>
+    <sheet name="성과지표" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -2873,4 +2875,448 @@
     <ignoredError numberStoredAsText="1" sqref="A1:J81"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D16"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>구분</v>
+      </c>
+      <c r="B1" t="str">
+        <v>항목</v>
+      </c>
+      <c r="C1" t="str">
+        <v>내용</v>
+      </c>
+      <c r="D1" t="str">
+        <v>비고</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>사업개요</v>
+      </c>
+      <c r="B2" t="str">
+        <v>사업명</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026 생태 탐험 캠프</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>사업개요</v>
+      </c>
+      <c r="B3" t="str">
+        <v>사업기간</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026. 5. ~ 2026. 6. (당일 프로그램 × 8회)</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>사업개요</v>
+      </c>
+      <c r="B4" t="str">
+        <v>참여대상</v>
+      </c>
+      <c r="C4" t="str">
+        <v>관내 초·중학생 80명</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>사업개요</v>
+      </c>
+      <c r="B5" t="str">
+        <v>사업예산</v>
+      </c>
+      <c r="C5" t="str">
+        <v>6,500천원</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>사업개요</v>
+      </c>
+      <c r="B6" t="str">
+        <v>추진부서</v>
+      </c>
+      <c r="C6" t="str">
+        <v>청소년환경교육팀</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>사업개요</v>
+      </c>
+      <c r="B7" t="str">
+        <v>추진배경</v>
+      </c>
+      <c r="C7" t="str">
+        <v>청소년의 자연 체험 기회 감소와 환경 감수성 저하 우려</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>사업개요</v>
+      </c>
+      <c r="B8" t="str">
+        <v>사업목적</v>
+      </c>
+      <c r="C8" t="str">
+        <v>생태 탐험 활동을 통해 청소년의 자연에 대한 흥미와 또래 협력 경험을 높인다</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>목표</v>
+      </c>
+      <c r="B9" t="str">
+        <v>추진목표</v>
+      </c>
+      <c r="C9" t="str">
+        <v>활동 흥미도와 협력 경험 확대</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>목표</v>
+      </c>
+      <c r="B10" t="str">
+        <v>추진목표</v>
+      </c>
+      <c r="C10" t="str">
+        <v>프로그램 추천 의향(NPS) 제고</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>논리모형</v>
+      </c>
+      <c r="B11" t="str">
+        <v>투입</v>
+      </c>
+      <c r="C11" t="str" xml:space="preserve">
+        <v xml:space="preserve">예산 6,500천원
+생태 해설사 4명
+인근 생태공원·수목원</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>논리모형</v>
+      </c>
+      <c r="B12" t="str">
+        <v>활동</v>
+      </c>
+      <c r="C12" t="str" xml:space="preserve">
+        <v xml:space="preserve">생태 탐사 8회
+모둠별 관찰일지 작성 8회</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>논리모형</v>
+      </c>
+      <c r="B13" t="str">
+        <v>산출</v>
+      </c>
+      <c r="C13" t="str" xml:space="preserve">
+        <v xml:space="preserve">프로그램 8회 운영
+참여 청소년 연인원 80명</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>논리모형</v>
+      </c>
+      <c r="B14" t="str">
+        <v>단기성과</v>
+      </c>
+      <c r="C14" t="str" xml:space="preserve">
+        <v xml:space="preserve">활동 흥미도 향상
+협력 기회 충분도 향상
+추천지수 제고</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>논리모형</v>
+      </c>
+      <c r="B15" t="str">
+        <v>중기성과</v>
+      </c>
+      <c r="C15" t="str">
+        <v>환경에 대한 관심 지속</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>논리모형</v>
+      </c>
+      <c r="B16" t="str">
+        <v>영향</v>
+      </c>
+      <c r="C16" t="str">
+        <v>자연과 공동체를 아끼는 청소년 성장</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>지표ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>지표명</v>
+      </c>
+      <c r="C1" t="str">
+        <v>성과단계</v>
+      </c>
+      <c r="D1" t="str">
+        <v>연계목표</v>
+      </c>
+      <c r="E1" t="str">
+        <v>측정방법</v>
+      </c>
+      <c r="F1" t="str">
+        <v>대상문항</v>
+      </c>
+      <c r="G1" t="str">
+        <v>목표값</v>
+      </c>
+      <c r="H1" t="str">
+        <v>실적값</v>
+      </c>
+      <c r="I1" t="str">
+        <v>방향</v>
+      </c>
+      <c r="J1" t="str">
+        <v>단위</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>K1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>프로그램 운영 횟수</v>
+      </c>
+      <c r="C2" t="str">
+        <v>산출</v>
+      </c>
+      <c r="D2" t="str">
+        <v>활동 흥미도와 협력 경험 확대</v>
+      </c>
+      <c r="E2" t="str">
+        <v>직접입력</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
+      </c>
+      <c r="I2" t="str">
+        <v>상향</v>
+      </c>
+      <c r="J2" t="str">
+        <v>회</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>K2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>참여 청소년 수(실인원)</v>
+      </c>
+      <c r="C3" t="str">
+        <v>산출</v>
+      </c>
+      <c r="D3" t="str">
+        <v>활동 흥미도와 협력 경험 확대</v>
+      </c>
+      <c r="E3" t="str">
+        <v>직접입력</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3">
+        <v>80</v>
+      </c>
+      <c r="H3">
+        <v>80</v>
+      </c>
+      <c r="I3" t="str">
+        <v>상향</v>
+      </c>
+      <c r="J3" t="str">
+        <v>명</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>K3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>활동 흥미도(100점 환산)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>단기성과</v>
+      </c>
+      <c r="D4" t="str">
+        <v>활동 흥미도와 협력 경험 확대</v>
+      </c>
+      <c r="E4" t="str">
+        <v>100점 환산</v>
+      </c>
+      <c r="F4" t="str">
+        <v>활동 내용이 흥미로웠다</v>
+      </c>
+      <c r="G4">
+        <v>80</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>상향</v>
+      </c>
+      <c r="J4" t="str">
+        <v>점</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>K4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>협력 기회 충분도(100점 환산)</v>
+      </c>
+      <c r="C5" t="str">
+        <v>단기성과</v>
+      </c>
+      <c r="D5" t="str">
+        <v>활동 흥미도와 협력 경험 확대</v>
+      </c>
+      <c r="E5" t="str">
+        <v>100점 환산</v>
+      </c>
+      <c r="F5" t="str">
+        <v>다른 친구들과 협력할 기회가 충분했다</v>
+      </c>
+      <c r="G5">
+        <v>78</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>상향</v>
+      </c>
+      <c r="J5" t="str">
+        <v>점</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>K5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>순추천지수(NPS)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>단기성과</v>
+      </c>
+      <c r="D6" t="str">
+        <v>프로그램 추천 의향(NPS) 제고</v>
+      </c>
+      <c r="E6" t="str">
+        <v>NPS</v>
+      </c>
+      <c r="F6" t="str">
+        <v>이 활동을 친구에게 추천할 의향(0~10점)</v>
+      </c>
+      <c r="G6">
+        <v>30</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>상향</v>
+      </c>
+      <c r="J6" t="str">
+        <v>점</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/samples/2026_생태탐험_7점척도_NPS.xlsx
+++ b/samples/2026_생태탐험_7점척도_NPS.xlsx
@@ -3120,7 +3120,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:M6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3153,6 +3153,15 @@
       <c r="J1" t="str">
         <v>단위</v>
       </c>
+      <c r="K1" t="str">
+        <v>근거ID</v>
+      </c>
+      <c r="L1" t="str">
+        <v>근거 적용 사유</v>
+      </c>
+      <c r="M1" t="str">
+        <v>원문 검토</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -3185,6 +3194,15 @@
       <c r="J2" t="str">
         <v>회</v>
       </c>
+      <c r="K2" t="str">
+        <v>oecd-results-framework</v>
+      </c>
+      <c r="L2" t="str">
+        <v>활동 산출과 참여자 성과를 구분해 지표의 성과단계를 해석하는 데 적용</v>
+      </c>
+      <c r="M2" t="str">
+        <v>예</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -3217,6 +3235,15 @@
       <c r="J3" t="str">
         <v>명</v>
       </c>
+      <c r="K3" t="str">
+        <v>oecd-results-framework</v>
+      </c>
+      <c r="L3" t="str">
+        <v>활동 산출과 참여자 성과를 구분해 지표의 성과단계를 해석하는 데 적용</v>
+      </c>
+      <c r="M3" t="str">
+        <v>예</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -3249,6 +3276,15 @@
       <c r="J4" t="str">
         <v>점</v>
       </c>
+      <c r="K4" t="str">
+        <v>oecd-evaluation-matrix</v>
+      </c>
+      <c r="L4" t="str">
+        <v>평가 질문인 만족도·추천 의향과 해당 설문 문항 및 산출 지표를 명시적으로 연결하는 데 적용</v>
+      </c>
+      <c r="M4" t="str">
+        <v>예</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -3281,6 +3317,15 @@
       <c r="J5" t="str">
         <v>점</v>
       </c>
+      <c r="K5" t="str">
+        <v>oecd-evaluation-matrix</v>
+      </c>
+      <c r="L5" t="str">
+        <v>평가 질문인 만족도·추천 의향과 해당 설문 문항 및 산출 지표를 명시적으로 연결하는 데 적용</v>
+      </c>
+      <c r="M5" t="str">
+        <v>예</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -3313,10 +3358,19 @@
       <c r="J6" t="str">
         <v>점</v>
       </c>
+      <c r="K6" t="str">
+        <v>oecd-evaluation-matrix</v>
+      </c>
+      <c r="L6" t="str">
+        <v>평가 질문인 만족도·추천 의향과 해당 설문 문항 및 산출 지표를 명시적으로 연결하는 데 적용</v>
+      </c>
+      <c r="M6" t="str">
+        <v>예</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
   </ignoredErrors>
 </worksheet>
 </file>